--- a/E-Commerce Web/Amazon/Test Suites/Non-Functional Testing Suite/Localization Tests.xlsx
+++ b/E-Commerce Web/Amazon/Test Suites/Non-Functional Testing Suite/Localization Tests.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>The volume measurement is not changed, ounces stay in every country. The severity of this problem is not really high and this also may depend on the person who places the product</t>
-  </si>
-  <si>
-    <t>Bug Report</t>
   </si>
   <si>
     <t xml:space="preserve">1. Enter the Amazon web site              2. Choose a product (a cable) </t>
@@ -187,20 +184,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -304,59 +293,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -658,34 +647,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="3"/>
@@ -696,35 +685,35 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="16" t="s">
+    <row r="2" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="10" t="s">
         <v>14</v>
       </c>
       <c r="M2" s="3"/>
@@ -734,18 +723,18 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="4" t="s">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="20"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="20"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="11"/>
       <c r="M3" s="3"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -753,18 +742,18 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="5" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="21"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="12"/>
       <c r="M4" s="3"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -772,101 +761,101 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="A5" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="14" t="s">
         <v>35</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
       <c r="F6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="12"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="14"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="12"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="12"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="14"/>
       <c r="K7" s="3"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:17" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="A8" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="13" t="s">
+      <c r="G8" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="10" t="s">
         <v>36</v>
       </c>
       <c r="K8" s="3"/>
@@ -874,108 +863,104 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
       <c r="F9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="20"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="3" t="s">
-        <v>37</v>
-      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="3"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
     <row r="10" spans="1:17" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="4" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="21"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="21"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="12"/>
       <c r="K10" s="3"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
     <row r="11" spans="1:17" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="10" t="s">
+      <c r="A11" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="F11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="10" t="s">
+      <c r="G11" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="11" t="s">
-        <v>52</v>
+      <c r="J11" s="19" t="s">
+        <v>51</v>
       </c>
       <c r="K11" s="3"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
     <row r="12" spans="1:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
       <c r="F12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="3" t="s">
-        <v>37</v>
-      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="3"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
     <row r="13" spans="1:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G13" s="12"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="11"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="19"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -984,36 +969,36 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="10" t="s">
+    <row r="14" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="10" t="s">
+      <c r="G14" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="11" t="s">
-        <v>53</v>
+      <c r="J14" s="19" t="s">
+        <v>52</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1024,21 +1009,19 @@
       <c r="Q14" s="2"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
       <c r="F15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="3" t="s">
-        <v>37</v>
-      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="2"/>
@@ -1047,18 +1030,18 @@
       <c r="Q15" s="2"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G16" s="12"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="11"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="19"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -1095,16 +1078,16 @@
       <c r="Q19" s="2"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="2"/>
@@ -1113,16 +1096,16 @@
       <c r="Q20" s="2"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="2"/>
@@ -1131,16 +1114,16 @@
       <c r="Q21" s="2"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="2"/>
@@ -1149,16 +1132,16 @@
       <c r="Q22" s="2"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="2"/>
@@ -1167,16 +1150,16 @@
       <c r="Q23" s="2"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
@@ -1186,16 +1169,16 @@
       <c r="Q24" s="2"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -1233,6 +1216,35 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="J11:J13"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="G2:G4"/>
     <mergeCell ref="J2:J4"/>
@@ -1249,35 +1261,6 @@
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="I8:I10"/>
-    <mergeCell ref="J8:J10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="J11:J13"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="G14:G16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
